--- a/branches/fix/release-demo-concurrency/all-profiles.xlsx
+++ b/branches/fix/release-demo-concurrency/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T05:15:25+00:00</t>
+    <t>2026-08-14T05:21:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
